--- a/astro-site/public/dl/guia-pasteleria-obrador/checklist-equipamiento-y-proveedores.xlsx
+++ b/astro-site/public/dl/guia-pasteleria-obrador/checklist-equipamiento-y-proveedores.xlsx
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BP-20</t>
+          <t>BE-20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
